--- a/erp-server/erp-server-mrp/src/main/resources/excel/calcHistorySaleQtyTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/calcHistorySaleQtyTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>SKU</t>
   </si>
@@ -42,21 +42,6 @@
   </si>
   <si>
     <t>销量</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.platform}</t>
-  </si>
-  <si>
-    <t>{.shopName}</t>
-  </si>
-  <si>
-    <t>{.billDate}</t>
-  </si>
-  <si>
-    <t>{.qty}</t>
   </si>
 </sst>
 </file>
@@ -1201,8 +1186,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.375" customWidth="1"/>
     <col min="2" max="2" width="18.625" customWidth="1"/>
@@ -1228,23 +1213,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
